--- a/upload/4M/1775039387747-List_Sales_Team_Feb_27th_2026.xlsx
+++ b/upload/4M/1775039387747-List_Sales_Team_Feb_27th_2026.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\A_suseri's\BC-BR\Personnel &amp; HR------------------------------\a_LISTES SALES TEAM\"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,60 +44,135 @@
     <t xml:space="preserve">Name </t>
   </si>
   <si>
+    <t>Localisation</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rattached to Plant </t>
+  </si>
+  <si>
     <t>Sales</t>
   </si>
   <si>
+    <t>ERIC SUSZYLO</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Nafta</t>
+  </si>
+  <si>
+    <t>Monterrey</t>
+  </si>
+  <si>
     <t>DEAN HAYWARD</t>
   </si>
   <si>
-    <t>ERIC SUSZYLO</t>
-  </si>
-  <si>
-    <t>USA</t>
+    <t>JAMES MCCRONE</t>
+  </si>
+  <si>
+    <t>Mexique</t>
   </si>
   <si>
     <t>FRANCK LAGADEC</t>
   </si>
   <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
     <t>Poitiers</t>
   </si>
   <si>
+    <t>MARTIN ZACNY</t>
+  </si>
+  <si>
     <t>Germany</t>
   </si>
   <si>
-    <t>MARTIN ZACNY</t>
-  </si>
-  <si>
-    <t>JAMES MCCRONE</t>
+    <t>Frankfurt</t>
+  </si>
+  <si>
+    <t>MARION SPICKER</t>
+  </si>
+  <si>
+    <t>Cyclam</t>
+  </si>
+  <si>
+    <t>SOUHEIL YAACOUBI</t>
+  </si>
+  <si>
+    <t>Tunisia</t>
+  </si>
+  <si>
+    <t>STS</t>
+  </si>
+  <si>
+    <t>RAMKUMAR PARTHASARATHI</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>South Asia</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>SELVAKUMAR KUMARESAN</t>
+  </si>
+  <si>
+    <t>VADIVUKKARASI SUBBRAMANIYAN</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER JOHN</t>
+  </si>
+  <si>
+    <t>2 Days/week from Feb 27th 2026</t>
   </si>
   <si>
     <t>EIPE THOMAS</t>
   </si>
   <si>
-    <t>India</t>
+    <t>PARIMMAL PATKKI</t>
+  </si>
+  <si>
+    <t>SAM JOO</t>
+  </si>
+  <si>
+    <t>Korea</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>JUNGHWAN YU</t>
+  </si>
+  <si>
+    <t>YOUNGJIN PARK</t>
   </si>
   <si>
     <t>TAO REN</t>
   </si>
   <si>
+    <t>China</t>
+  </si>
+  <si>
     <t>Kunshan</t>
   </si>
   <si>
     <t>ALICE CHEN</t>
   </si>
   <si>
-    <t>JUNGHWAN YU</t>
-  </si>
-  <si>
-    <t>Korea</t>
-  </si>
-  <si>
-    <t>MARION SPICKER</t>
-  </si>
-  <si>
-    <t>Cyclam</t>
-  </si>
-  <si>
     <t>ALLEN TAO</t>
   </si>
   <si>
@@ -107,95 +182,20 @@
     <t>AUSTIN YUAN</t>
   </si>
   <si>
+    <t>WILLIAM REN</t>
+  </si>
+  <si>
     <t>FELIX WANG</t>
   </si>
   <si>
     <t>Tianjin</t>
-  </si>
-  <si>
-    <t>PARIMMAL PATKKI</t>
-  </si>
-  <si>
-    <t>YOUNGJIN PARK</t>
-  </si>
-  <si>
-    <t>RAMKUMAR PARTHASARATHI</t>
-  </si>
-  <si>
-    <t>SELVAKUMAR KUMARESAN</t>
-  </si>
-  <si>
-    <t>SOUHEIL YAACOUBI</t>
-  </si>
-  <si>
-    <t>STS</t>
-  </si>
-  <si>
-    <t>VADIVUKKARASI SUBBRAMANIYAN</t>
-  </si>
-  <si>
-    <t>CHRISTOPHER JOHN</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Nafta</t>
-  </si>
-  <si>
-    <t>Monterrey</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>Frankfurt</t>
-  </si>
-  <si>
-    <t>Chennai</t>
-  </si>
-  <si>
-    <t>China</t>
-  </si>
-  <si>
-    <t>WILLIAM REN</t>
-  </si>
-  <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Localisation</t>
-  </si>
-  <si>
-    <t>Mexique</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Tunisia</t>
-  </si>
-  <si>
-    <t>South Asia</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Rattached to Plant </t>
-  </si>
-  <si>
-    <t>SAM JOO</t>
-  </si>
-  <si>
-    <t>2 Days/week from Feb 27th 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -719,16 +719,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="28.1796875" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="1"/>
-    <col min="3" max="3" width="30.36328125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="18.54296875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.08984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" style="1"/>
+    <col min="3" max="3" width="30.42578125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="18.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" s="12" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
@@ -736,407 +736,407 @@
         <v>1</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickTop="1">
+      <c r="B3" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="15" t="s">
+      <c r="E19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B4" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="D24" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="4" t="s">
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B10" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B12" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B13" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="16" t="s">
+      <c r="F25" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B15" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B16" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B19" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B21" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B22" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B23" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B24" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
